--- a/splists_raw/ParqueMetropolitano/PNM_Listas_Especies.xlsx
+++ b/splists_raw/ParqueMetropolitano/PNM_Listas_Especies.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CamposEG\Documents\BRAHMS\Exports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mullerh\Dropbox (Personal)\ForestGEO\SPLISTS\PNMplantsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3601C245-D9FF-402C-9001-476EFD90A3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D34A9B-1788-4D9A-A39F-D801FB5D9A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15420" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Correa et al., 2010" sheetId="3" r:id="rId1"/>
     <sheet name="Campos-Pineda et al., 2014" sheetId="2" r:id="rId2"/>
     <sheet name="Correa et al., 2019" sheetId="1" r:id="rId3"/>
     <sheet name="SCZ Herbarium" sheetId="4" r:id="rId4"/>
+    <sheet name="info" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Correa et al., 2019'!$A$1:$I$203</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3136" uniqueCount="1152">
   <si>
     <t>FamilyName</t>
   </si>
@@ -3471,13 +3472,37 @@
   </si>
   <si>
     <t>Especie</t>
+  </si>
+  <si>
+    <t>Le adjunto el archivo con varios listados de especies (en hojas separadas) utilizando como fuentes:</t>
+  </si>
+  <si>
+    <t>Correa, M., Stapf, M., De Sedas, A., Hernández, F., Carranza, R. 2010. Árboles y arbustos del Parque Natural Metropolitano, Panamá. </t>
+  </si>
+  <si>
+    <t>Campos-Pineda, E.,  Moreno, J. &amp; Mendieta, J. 2014. Análisis florístico de la vegetación arbórea de una parcela de bosque en el Parque Natural Metropolitano, Provincia de Panamá.</t>
+  </si>
+  <si>
+    <t>Correa, M., Galdames, C. &amp; Campos-Pineda, E. 2019. Hierbas, bejucos y lianas en el Parque Natural Metropolitano, Panamá.</t>
+  </si>
+  <si>
+    <t>Especímenes depositados en el Herbario SCZ, extraído de la base de datos.</t>
+  </si>
+  <si>
+    <t>This file was created by Ernesto Campos</t>
+  </si>
+  <si>
+    <t>Emailed from Ernesto Campos to Helene Muller-Landau on August 12, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associated text explaining the file:  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3492,6 +3517,18 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -3522,7 +3559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3530,6 +3567,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14795,4 +14839,57 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DB31A3-D41E-4019-97A9-A14C74BEB1AE}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+    </row>
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>